--- a/src/results/cr/cross_tab_wage.xlsx
+++ b/src/results/cr/cross_tab_wage.xlsx
@@ -446,7 +446,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G76"/>
+  <dimension ref="A1:G90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -494,1575 +494,1608 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>P Inc</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>62</v>
+          <t>P Inc -15</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="n">
+        <v>15</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="F3" t="n">
-        <v>26</v>
+        <v>7</v>
+      </c>
+      <c r="F3" s="2" t="n">
+        <v>8</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>P Comp</t>
+          <t>P Inc +15</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>310</v>
+        <v>115</v>
       </c>
       <c r="C4" t="n">
+        <v>25</v>
+      </c>
+      <c r="D4" t="n">
+        <v>21</v>
+      </c>
+      <c r="E4" t="n">
+        <v>38</v>
+      </c>
+      <c r="F4" t="n">
         <v>39</v>
       </c>
-      <c r="D4" t="n">
-        <v>39</v>
-      </c>
-      <c r="E4" t="n">
-        <v>40</v>
-      </c>
-      <c r="F4" t="n">
-        <v>68</v>
-      </c>
       <c r="G4" t="n">
-        <v>37</v>
+        <v>31</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>S Inc -15</t>
+          <t>P Comp -15</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>150</v>
+        <v>144</v>
       </c>
       <c r="C5" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="D5" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="E5" s="2" t="n">
         <v>17</v>
       </c>
-      <c r="D5" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="E5" s="2" t="n">
-        <v>16</v>
-      </c>
       <c r="F5" t="n">
-        <v>23</v>
-      </c>
-      <c r="G5" s="2" t="n">
-        <v>16</v>
+        <v>49</v>
+      </c>
+      <c r="G5" t="n">
+        <v>30</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>S Inc+15</t>
+          <t>P Comp +15</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>244</v>
+        <v>472</v>
       </c>
       <c r="C6" t="n">
-        <v>33</v>
+        <v>81</v>
       </c>
       <c r="D6" t="n">
-        <v>22</v>
-      </c>
-      <c r="E6" s="2" t="n">
-        <v>20</v>
+        <v>69</v>
+      </c>
+      <c r="E6" t="n">
+        <v>90</v>
       </c>
       <c r="F6" t="n">
-        <v>25</v>
-      </c>
-      <c r="G6" s="2" t="n">
-        <v>13</v>
+        <v>90</v>
+      </c>
+      <c r="G6" t="n">
+        <v>64</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>S Comp -15</t>
+          <t>S Inc -15</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>297</v>
+        <v>302</v>
       </c>
       <c r="C7" t="n">
-        <v>22</v>
+        <v>43</v>
       </c>
       <c r="D7" t="n">
-        <v>24</v>
+        <v>43</v>
       </c>
       <c r="E7" t="n">
-        <v>36</v>
+        <v>57</v>
       </c>
       <c r="F7" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="G7" t="n">
-        <v>29</v>
+        <v>48</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>S Comp +15</t>
+          <t>S Inc+15</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>195</v>
+        <v>301</v>
       </c>
       <c r="C8" t="n">
-        <v>28</v>
-      </c>
-      <c r="D8" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="E8" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="F8" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="G8" s="2" t="n">
-        <v>10</v>
+        <v>45</v>
+      </c>
+      <c r="D8" t="n">
+        <v>40</v>
+      </c>
+      <c r="E8" t="n">
+        <v>32</v>
+      </c>
+      <c r="F8" t="n">
+        <v>35</v>
+      </c>
+      <c r="G8" t="n">
+        <v>25</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Ter -15</t>
+          <t>S Comp -15</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>701</v>
+        <v>357</v>
       </c>
       <c r="C9" t="n">
-        <v>61</v>
+        <v>39</v>
       </c>
       <c r="D9" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E9" t="n">
-        <v>56</v>
+        <v>38</v>
       </c>
       <c r="F9" t="n">
-        <v>56</v>
+        <v>42</v>
       </c>
       <c r="G9" t="n">
-        <v>37</v>
+        <v>33</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>S Comp +15</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>261</v>
+      </c>
+      <c r="C10" t="n">
+        <v>40</v>
+      </c>
+      <c r="D10" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="E10" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="F10" t="n">
+        <v>29</v>
+      </c>
+      <c r="G10" s="2" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Ter -15</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>623</v>
+      </c>
+      <c r="C11" t="n">
+        <v>43</v>
+      </c>
+      <c r="D11" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="E11" t="n">
+        <v>48</v>
+      </c>
+      <c r="F11" t="n">
+        <v>41</v>
+      </c>
+      <c r="G11" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
           <t>Ter +15</t>
         </is>
       </c>
-      <c r="B10" t="n">
-        <v>440</v>
-      </c>
-      <c r="C10" t="n">
-        <v>64</v>
-      </c>
-      <c r="D10" t="n">
-        <v>31</v>
-      </c>
-      <c r="E10" t="n">
+      <c r="B12" t="n">
+        <v>432</v>
+      </c>
+      <c r="C12" t="n">
         <v>42</v>
       </c>
-      <c r="F10" t="n">
-        <v>40</v>
-      </c>
-      <c r="G10" t="n">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
+      <c r="D12" t="n">
+        <v>26</v>
+      </c>
+      <c r="E12" t="n">
+        <v>26</v>
+      </c>
+      <c r="F12" t="n">
+        <v>21</v>
+      </c>
+      <c r="G12" s="2" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
         <v>2016</v>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
         <is>
           <t>habilidad</t>
         </is>
       </c>
-      <c r="B13" s="1" t="inlineStr">
+      <c r="B15" s="1" t="inlineStr">
         <is>
           <t>Central</t>
         </is>
       </c>
-      <c r="C13" s="1" t="inlineStr">
+      <c r="C15" s="1" t="inlineStr">
         <is>
           <t>Chorotega</t>
         </is>
       </c>
-      <c r="D13" s="1" t="inlineStr">
+      <c r="D15" s="1" t="inlineStr">
         <is>
           <t>Pacífico Central</t>
         </is>
       </c>
-      <c r="E13" s="1" t="inlineStr">
+      <c r="E15" s="1" t="inlineStr">
         <is>
           <t>Brunca</t>
         </is>
       </c>
-      <c r="F13" s="1" t="inlineStr">
+      <c r="F15" s="1" t="inlineStr">
         <is>
           <t>Huetar Caribe</t>
         </is>
       </c>
-      <c r="G13" s="1" t="inlineStr">
+      <c r="G15" s="1" t="inlineStr">
         <is>
           <t>Huetar Norte</t>
         </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>P Inc</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>58</v>
-      </c>
-      <c r="C14" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="D14" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="E14" s="2" t="n">
-        <v>19</v>
-      </c>
-      <c r="F14" t="n">
-        <v>21</v>
-      </c>
-      <c r="G14" s="2" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>P Comp</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>361</v>
-      </c>
-      <c r="C15" t="n">
-        <v>47</v>
-      </c>
-      <c r="D15" t="n">
-        <v>36</v>
-      </c>
-      <c r="E15" t="n">
-        <v>50</v>
-      </c>
-      <c r="F15" t="n">
-        <v>62</v>
-      </c>
-      <c r="G15" t="n">
-        <v>40</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>S Inc -15</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>140</v>
+          <t>P Inc -15</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>8</v>
       </c>
       <c r="C16" s="2" t="n">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>S Inc+15</t>
+          <t>P Inc +15</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>201</v>
-      </c>
-      <c r="C17" t="n">
-        <v>21</v>
-      </c>
-      <c r="D17" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="C17" s="2" t="n">
         <v>18</v>
       </c>
-      <c r="E17" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="F17" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="G17" s="2" t="n">
-        <v>14</v>
+      <c r="D17" t="n">
+        <v>27</v>
+      </c>
+      <c r="E17" t="n">
+        <v>32</v>
+      </c>
+      <c r="F17" t="n">
+        <v>58</v>
+      </c>
+      <c r="G17" t="n">
+        <v>34</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>S Comp -15</t>
+          <t>P Comp -15</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>323</v>
-      </c>
-      <c r="C18" t="n">
-        <v>28</v>
-      </c>
-      <c r="D18" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="E18" t="n">
-        <v>31</v>
+        <v>138</v>
+      </c>
+      <c r="C18" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="D18" t="n">
+        <v>22</v>
+      </c>
+      <c r="E18" s="2" t="n">
+        <v>17</v>
       </c>
       <c r="F18" t="n">
+        <v>36</v>
+      </c>
+      <c r="G18" t="n">
         <v>23</v>
-      </c>
-      <c r="G18" t="n">
-        <v>31</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>S Comp +15</t>
+          <t>P Comp +15</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>203</v>
+        <v>486</v>
       </c>
       <c r="C19" t="n">
-        <v>38</v>
-      </c>
-      <c r="D19" s="2" t="n">
-        <v>19</v>
-      </c>
-      <c r="E19" s="2" t="n">
-        <v>15</v>
+        <v>80</v>
+      </c>
+      <c r="D19" t="n">
+        <v>55</v>
+      </c>
+      <c r="E19" t="n">
+        <v>82</v>
       </c>
       <c r="F19" t="n">
-        <v>22</v>
-      </c>
-      <c r="G19" s="2" t="n">
-        <v>5</v>
+        <v>101</v>
+      </c>
+      <c r="G19" t="n">
+        <v>75</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Ter -15</t>
+          <t>S Inc -15</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>670</v>
+        <v>303</v>
       </c>
       <c r="C20" t="n">
-        <v>68</v>
+        <v>44</v>
       </c>
       <c r="D20" t="n">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="E20" t="n">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="F20" t="n">
-        <v>50</v>
+        <v>62</v>
       </c>
       <c r="G20" t="n">
-        <v>33</v>
+        <v>57</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Ter +15</t>
+          <t>S Inc+15</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>465</v>
+        <v>299</v>
       </c>
       <c r="C21" t="n">
-        <v>56</v>
+        <v>40</v>
       </c>
       <c r="D21" t="n">
+        <v>31</v>
+      </c>
+      <c r="E21" t="n">
+        <v>28</v>
+      </c>
+      <c r="F21" t="n">
+        <v>41</v>
+      </c>
+      <c r="G21" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>S Comp -15</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>357</v>
+      </c>
+      <c r="C22" t="n">
+        <v>50</v>
+      </c>
+      <c r="D22" t="n">
+        <v>31</v>
+      </c>
+      <c r="E22" t="n">
+        <v>48</v>
+      </c>
+      <c r="F22" t="n">
+        <v>39</v>
+      </c>
+      <c r="G22" t="n">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>S Comp +15</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>258</v>
+      </c>
+      <c r="C23" t="n">
+        <v>42</v>
+      </c>
+      <c r="D23" t="n">
+        <v>31</v>
+      </c>
+      <c r="E23" t="n">
+        <v>31</v>
+      </c>
+      <c r="F23" t="n">
+        <v>39</v>
+      </c>
+      <c r="G23" s="2" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Ter -15</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>561</v>
+      </c>
+      <c r="C24" t="n">
+        <v>48</v>
+      </c>
+      <c r="D24" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="E24" t="n">
+        <v>57</v>
+      </c>
+      <c r="F24" t="n">
         <v>37</v>
       </c>
-      <c r="E21" t="n">
-        <v>41</v>
-      </c>
-      <c r="F21" t="n">
-        <v>27</v>
-      </c>
-      <c r="G21" s="2" t="n">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>2017</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="1" t="inlineStr">
-        <is>
-          <t>habilidad</t>
-        </is>
-      </c>
-      <c r="B24" s="1" t="inlineStr">
-        <is>
-          <t>Central</t>
-        </is>
-      </c>
-      <c r="C24" s="1" t="inlineStr">
-        <is>
-          <t>Chorotega</t>
-        </is>
-      </c>
-      <c r="D24" s="1" t="inlineStr">
-        <is>
-          <t>Pacífico Central</t>
-        </is>
-      </c>
-      <c r="E24" s="1" t="inlineStr">
-        <is>
-          <t>Brunca</t>
-        </is>
-      </c>
-      <c r="F24" s="1" t="inlineStr">
-        <is>
-          <t>Huetar Caribe</t>
-        </is>
-      </c>
-      <c r="G24" s="1" t="inlineStr">
-        <is>
-          <t>Huetar Norte</t>
-        </is>
+      <c r="G24" t="n">
+        <v>22</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>P Inc</t>
+          <t>Ter +15</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>54</v>
-      </c>
-      <c r="C25" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="D25" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="E25" s="2" t="n">
-        <v>10</v>
+        <v>429</v>
+      </c>
+      <c r="C25" t="n">
+        <v>51</v>
+      </c>
+      <c r="D25" t="n">
+        <v>22</v>
+      </c>
+      <c r="E25" t="n">
+        <v>28</v>
       </c>
       <c r="F25" t="n">
-        <v>23</v>
-      </c>
-      <c r="G25" s="2" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>P Comp</t>
-        </is>
-      </c>
-      <c r="B26" t="n">
-        <v>286</v>
-      </c>
-      <c r="C26" t="n">
-        <v>31</v>
-      </c>
-      <c r="D26" t="n">
-        <v>33</v>
-      </c>
-      <c r="E26" t="n">
-        <v>47</v>
-      </c>
-      <c r="F26" t="n">
-        <v>48</v>
-      </c>
-      <c r="G26" t="n">
-        <v>29</v>
+        <v>21</v>
+      </c>
+      <c r="G25" t="n">
+        <v>22</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>S Inc -15</t>
-        </is>
-      </c>
-      <c r="B27" t="n">
-        <v>143</v>
-      </c>
-      <c r="C27" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="D27" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="E27" t="n">
-        <v>23</v>
-      </c>
-      <c r="F27" t="n">
-        <v>24</v>
-      </c>
-      <c r="G27" s="2" t="n">
-        <v>15</v>
+      <c r="A27" t="n">
+        <v>2017</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>S Inc+15</t>
-        </is>
-      </c>
-      <c r="B28" t="n">
-        <v>199</v>
-      </c>
-      <c r="C28" t="n">
-        <v>26</v>
-      </c>
-      <c r="D28" s="2" t="n">
-        <v>19</v>
-      </c>
-      <c r="E28" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="F28" t="n">
-        <v>27</v>
-      </c>
-      <c r="G28" t="n">
-        <v>21</v>
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>habilidad</t>
+        </is>
+      </c>
+      <c r="B28" s="1" t="inlineStr">
+        <is>
+          <t>Central</t>
+        </is>
+      </c>
+      <c r="C28" s="1" t="inlineStr">
+        <is>
+          <t>Chorotega</t>
+        </is>
+      </c>
+      <c r="D28" s="1" t="inlineStr">
+        <is>
+          <t>Pacífico Central</t>
+        </is>
+      </c>
+      <c r="E28" s="1" t="inlineStr">
+        <is>
+          <t>Brunca</t>
+        </is>
+      </c>
+      <c r="F28" s="1" t="inlineStr">
+        <is>
+          <t>Huetar Caribe</t>
+        </is>
+      </c>
+      <c r="G28" s="1" t="inlineStr">
+        <is>
+          <t>Huetar Norte</t>
+        </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>S Comp -15</t>
-        </is>
-      </c>
-      <c r="B29" t="n">
-        <v>287</v>
-      </c>
-      <c r="C29" t="n">
-        <v>33</v>
-      </c>
-      <c r="D29" t="n">
-        <v>21</v>
-      </c>
-      <c r="E29" t="n">
-        <v>25</v>
-      </c>
-      <c r="F29" t="n">
-        <v>28</v>
+          <t>P Inc -15</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="C29" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D29" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E29" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="F29" s="2" t="n">
+        <v>8</v>
       </c>
       <c r="G29" s="2" t="n">
-        <v>20</v>
+        <v>7</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>S Comp +15</t>
+          <t>P Inc +15</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>180</v>
-      </c>
-      <c r="C30" t="n">
-        <v>35</v>
+        <v>83</v>
+      </c>
+      <c r="C30" s="2" t="n">
+        <v>19</v>
       </c>
       <c r="D30" t="n">
-        <v>28</v>
-      </c>
-      <c r="E30" s="2" t="n">
-        <v>17</v>
+        <v>25</v>
+      </c>
+      <c r="E30" t="n">
+        <v>37</v>
       </c>
       <c r="F30" t="n">
-        <v>22</v>
-      </c>
-      <c r="G30" s="2" t="n">
-        <v>10</v>
+        <v>42</v>
+      </c>
+      <c r="G30" t="n">
+        <v>26</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Ter -15</t>
+          <t>P Comp -15</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>601</v>
-      </c>
-      <c r="C31" t="n">
-        <v>57</v>
-      </c>
-      <c r="D31" t="n">
-        <v>38</v>
-      </c>
-      <c r="E31" t="n">
-        <v>55</v>
+        <v>133</v>
+      </c>
+      <c r="C31" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="D31" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="E31" s="2" t="n">
+        <v>11</v>
       </c>
       <c r="F31" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="G31" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Ter +15</t>
+          <t>P Comp +15</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>471</v>
+        <v>458</v>
       </c>
       <c r="C32" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D32" t="n">
-        <v>31</v>
+        <v>47</v>
       </c>
       <c r="E32" t="n">
+        <v>90</v>
+      </c>
+      <c r="F32" t="n">
+        <v>105</v>
+      </c>
+      <c r="G32" t="n">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>S Inc -15</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>287</v>
+      </c>
+      <c r="C33" t="n">
+        <v>51</v>
+      </c>
+      <c r="D33" t="n">
+        <v>34</v>
+      </c>
+      <c r="E33" t="n">
+        <v>46</v>
+      </c>
+      <c r="F33" t="n">
+        <v>49</v>
+      </c>
+      <c r="G33" t="n">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>S Inc+15</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>282</v>
+      </c>
+      <c r="C34" t="n">
+        <v>52</v>
+      </c>
+      <c r="D34" t="n">
+        <v>29</v>
+      </c>
+      <c r="E34" t="n">
+        <v>33</v>
+      </c>
+      <c r="F34" t="n">
+        <v>50</v>
+      </c>
+      <c r="G34" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>S Comp -15</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>356</v>
+      </c>
+      <c r="C35" t="n">
+        <v>55</v>
+      </c>
+      <c r="D35" t="n">
+        <v>32</v>
+      </c>
+      <c r="E35" t="n">
+        <v>45</v>
+      </c>
+      <c r="F35" t="n">
+        <v>57</v>
+      </c>
+      <c r="G35" t="n">
         <v>40</v>
-      </c>
-      <c r="F32" t="n">
-        <v>29</v>
-      </c>
-      <c r="G32" s="2" t="n">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="n">
-        <v>2018</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="1" t="inlineStr">
-        <is>
-          <t>habilidad</t>
-        </is>
-      </c>
-      <c r="B35" s="1" t="inlineStr">
-        <is>
-          <t>Central</t>
-        </is>
-      </c>
-      <c r="C35" s="1" t="inlineStr">
-        <is>
-          <t>Chorotega</t>
-        </is>
-      </c>
-      <c r="D35" s="1" t="inlineStr">
-        <is>
-          <t>Pacífico Central</t>
-        </is>
-      </c>
-      <c r="E35" s="1" t="inlineStr">
-        <is>
-          <t>Brunca</t>
-        </is>
-      </c>
-      <c r="F35" s="1" t="inlineStr">
-        <is>
-          <t>Huetar Caribe</t>
-        </is>
-      </c>
-      <c r="G35" s="1" t="inlineStr">
-        <is>
-          <t>Huetar Norte</t>
-        </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>P Inc</t>
+          <t>S Comp +15</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>51</v>
-      </c>
-      <c r="C36" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="D36" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="E36" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="F36" s="2" t="n">
-        <v>13</v>
+        <v>254</v>
+      </c>
+      <c r="C36" t="n">
+        <v>37</v>
+      </c>
+      <c r="D36" t="n">
+        <v>25</v>
+      </c>
+      <c r="E36" t="n">
+        <v>26</v>
+      </c>
+      <c r="F36" t="n">
+        <v>35</v>
       </c>
       <c r="G36" s="2" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>P Comp</t>
+          <t>Ter -15</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>246</v>
+        <v>492</v>
       </c>
       <c r="C37" t="n">
         <v>37</v>
       </c>
       <c r="D37" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E37" t="n">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="F37" t="n">
-        <v>51</v>
-      </c>
-      <c r="G37" t="n">
-        <v>32</v>
+        <v>42</v>
+      </c>
+      <c r="G37" s="2" t="n">
+        <v>20</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>S Inc -15</t>
+          <t>Ter +15</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>119</v>
-      </c>
-      <c r="C38" s="2" t="n">
-        <v>18</v>
+        <v>415</v>
+      </c>
+      <c r="C38" t="n">
+        <v>49</v>
       </c>
       <c r="D38" s="2" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="E38" t="n">
-        <v>21</v>
-      </c>
-      <c r="F38" s="2" t="n">
-        <v>15</v>
+        <v>36</v>
+      </c>
+      <c r="F38" t="n">
+        <v>23</v>
       </c>
       <c r="G38" s="2" t="n">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>S Inc+15</t>
-        </is>
-      </c>
-      <c r="B39" t="n">
-        <v>210</v>
-      </c>
-      <c r="C39" t="n">
-        <v>26</v>
-      </c>
-      <c r="D39" t="n">
-        <v>30</v>
-      </c>
-      <c r="E39" t="n">
-        <v>23</v>
-      </c>
-      <c r="F39" t="n">
-        <v>23</v>
-      </c>
-      <c r="G39" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>S Comp -15</t>
-        </is>
-      </c>
-      <c r="B40" t="n">
-        <v>294</v>
-      </c>
-      <c r="C40" t="n">
-        <v>30</v>
-      </c>
-      <c r="D40" t="n">
-        <v>23</v>
-      </c>
-      <c r="E40" t="n">
-        <v>34</v>
-      </c>
-      <c r="F40" t="n">
-        <v>35</v>
-      </c>
-      <c r="G40" s="2" t="n">
-        <v>15</v>
+      <c r="A40" t="n">
+        <v>2018</v>
       </c>
     </row>
     <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>S Comp +15</t>
-        </is>
-      </c>
-      <c r="B41" t="n">
-        <v>175</v>
-      </c>
-      <c r="C41" t="n">
-        <v>35</v>
-      </c>
-      <c r="D41" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="E41" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="F41" t="n">
-        <v>25</v>
-      </c>
-      <c r="G41" s="2" t="n">
-        <v>17</v>
+      <c r="A41" s="1" t="inlineStr">
+        <is>
+          <t>habilidad</t>
+        </is>
+      </c>
+      <c r="B41" s="1" t="inlineStr">
+        <is>
+          <t>Central</t>
+        </is>
+      </c>
+      <c r="C41" s="1" t="inlineStr">
+        <is>
+          <t>Chorotega</t>
+        </is>
+      </c>
+      <c r="D41" s="1" t="inlineStr">
+        <is>
+          <t>Pacífico Central</t>
+        </is>
+      </c>
+      <c r="E41" s="1" t="inlineStr">
+        <is>
+          <t>Brunca</t>
+        </is>
+      </c>
+      <c r="F41" s="1" t="inlineStr">
+        <is>
+          <t>Huetar Caribe</t>
+        </is>
+      </c>
+      <c r="G41" s="1" t="inlineStr">
+        <is>
+          <t>Huetar Norte</t>
+        </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Ter -15</t>
-        </is>
-      </c>
-      <c r="B42" t="n">
-        <v>615</v>
-      </c>
-      <c r="C42" t="n">
-        <v>58</v>
-      </c>
-      <c r="D42" t="n">
-        <v>38</v>
-      </c>
-      <c r="E42" t="n">
-        <v>62</v>
-      </c>
-      <c r="F42" t="n">
-        <v>47</v>
-      </c>
-      <c r="G42" t="n">
-        <v>36</v>
+          <t>P Inc -15</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="C42" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D42" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E42" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F42" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G42" s="2" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Ter +15</t>
+          <t>P Inc +15</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>516</v>
-      </c>
-      <c r="C43" t="n">
-        <v>58</v>
+        <v>88</v>
+      </c>
+      <c r="C43" s="2" t="n">
+        <v>17</v>
       </c>
       <c r="D43" t="n">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="E43" t="n">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="F43" t="n">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="G43" t="n">
-        <v>23</v>
+        <v>32</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>P Comp -15</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>112</v>
+      </c>
+      <c r="C44" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="D44" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="E44" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="F44" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="G44" t="n">
+        <v>25</v>
       </c>
     </row>
     <row r="45">
-      <c r="A45" t="n">
-        <v>2019</v>
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>P Comp +15</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>410</v>
+      </c>
+      <c r="C45" t="n">
+        <v>69</v>
+      </c>
+      <c r="D45" t="n">
+        <v>54</v>
+      </c>
+      <c r="E45" t="n">
+        <v>74</v>
+      </c>
+      <c r="F45" t="n">
+        <v>98</v>
+      </c>
+      <c r="G45" t="n">
+        <v>54</v>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="inlineStr">
-        <is>
-          <t>habilidad</t>
-        </is>
-      </c>
-      <c r="B46" s="1" t="inlineStr">
-        <is>
-          <t>Central</t>
-        </is>
-      </c>
-      <c r="C46" s="1" t="inlineStr">
-        <is>
-          <t>Chorotega</t>
-        </is>
-      </c>
-      <c r="D46" s="1" t="inlineStr">
-        <is>
-          <t>Pacífico Central</t>
-        </is>
-      </c>
-      <c r="E46" s="1" t="inlineStr">
-        <is>
-          <t>Brunca</t>
-        </is>
-      </c>
-      <c r="F46" s="1" t="inlineStr">
-        <is>
-          <t>Huetar Caribe</t>
-        </is>
-      </c>
-      <c r="G46" s="1" t="inlineStr">
-        <is>
-          <t>Huetar Norte</t>
-        </is>
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>S Inc -15</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>284</v>
+      </c>
+      <c r="C46" t="n">
+        <v>54</v>
+      </c>
+      <c r="D46" t="n">
+        <v>32</v>
+      </c>
+      <c r="E46" t="n">
+        <v>40</v>
+      </c>
+      <c r="F46" t="n">
+        <v>61</v>
+      </c>
+      <c r="G46" t="n">
+        <v>54</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>P Inc</t>
+          <t>S Inc+15</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>39</v>
-      </c>
-      <c r="C47" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="D47" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="E47" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="F47" s="2" t="n">
-        <v>12</v>
+        <v>291</v>
+      </c>
+      <c r="C47" t="n">
+        <v>52</v>
+      </c>
+      <c r="D47" t="n">
+        <v>33</v>
+      </c>
+      <c r="E47" t="n">
+        <v>29</v>
+      </c>
+      <c r="F47" t="n">
+        <v>40</v>
       </c>
       <c r="G47" s="2" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>P Comp</t>
+          <t>S Comp -15</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>243</v>
+        <v>348</v>
       </c>
       <c r="C48" t="n">
-        <v>45</v>
+        <v>62</v>
       </c>
       <c r="D48" t="n">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="E48" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F48" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="G48" t="n">
-        <v>31</v>
+        <v>52</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>S Inc -15</t>
+          <t>S Comp +15</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>111</v>
-      </c>
-      <c r="C49" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="D49" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="E49" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="F49" s="2" t="n">
+        <v>267</v>
+      </c>
+      <c r="C49" t="n">
+        <v>36</v>
+      </c>
+      <c r="D49" t="n">
+        <v>32</v>
+      </c>
+      <c r="E49" t="n">
+        <v>38</v>
+      </c>
+      <c r="F49" t="n">
+        <v>39</v>
+      </c>
+      <c r="G49" s="2" t="n">
         <v>18</v>
-      </c>
-      <c r="G49" s="2" t="n">
-        <v>20</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>S Inc+15</t>
+          <t>Ter -15</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>199</v>
+        <v>529</v>
       </c>
       <c r="C50" t="n">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="D50" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="E50" t="n">
+        <v>33</v>
+      </c>
+      <c r="F50" t="n">
+        <v>29</v>
+      </c>
+      <c r="G50" t="n">
         <v>23</v>
-      </c>
-      <c r="F50" t="n">
-        <v>33</v>
-      </c>
-      <c r="G50" t="n">
-        <v>26</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>S Comp -15</t>
+          <t>Ter +15</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>272</v>
+        <v>440</v>
       </c>
       <c r="C51" t="n">
-        <v>36</v>
-      </c>
-      <c r="D51" s="2" t="n">
-        <v>17</v>
+        <v>53</v>
+      </c>
+      <c r="D51" t="n">
+        <v>23</v>
       </c>
       <c r="E51" t="n">
-        <v>37</v>
-      </c>
-      <c r="F51" t="n">
-        <v>36</v>
-      </c>
-      <c r="G51" t="n">
+        <v>26</v>
+      </c>
+      <c r="F51" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="G51" s="2" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>2019</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="1" t="inlineStr">
+        <is>
+          <t>habilidad</t>
+        </is>
+      </c>
+      <c r="B54" s="1" t="inlineStr">
+        <is>
+          <t>Central</t>
+        </is>
+      </c>
+      <c r="C54" s="1" t="inlineStr">
+        <is>
+          <t>Chorotega</t>
+        </is>
+      </c>
+      <c r="D54" s="1" t="inlineStr">
+        <is>
+          <t>Pacífico Central</t>
+        </is>
+      </c>
+      <c r="E54" s="1" t="inlineStr">
+        <is>
+          <t>Brunca</t>
+        </is>
+      </c>
+      <c r="F54" s="1" t="inlineStr">
+        <is>
+          <t>Huetar Caribe</t>
+        </is>
+      </c>
+      <c r="G54" s="1" t="inlineStr">
+        <is>
+          <t>Huetar Norte</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>P Inc -15</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="C55" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="D55" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E55" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F55" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="G55" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>P Inc +15</t>
+        </is>
+      </c>
+      <c r="B56" t="n">
+        <v>65</v>
+      </c>
+      <c r="C56" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="D56" t="n">
+        <v>23</v>
+      </c>
+      <c r="E56" t="n">
+        <v>28</v>
+      </c>
+      <c r="F56" t="n">
+        <v>40</v>
+      </c>
+      <c r="G56" t="n">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>P Comp -15</t>
+        </is>
+      </c>
+      <c r="B57" t="n">
+        <v>110</v>
+      </c>
+      <c r="C57" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="D57" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="E57" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="F57" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="G57" t="n">
         <v>25</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>S Comp +15</t>
-        </is>
-      </c>
-      <c r="B52" t="n">
-        <v>209</v>
-      </c>
-      <c r="C52" t="n">
-        <v>29</v>
-      </c>
-      <c r="D52" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="E52" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="F52" t="n">
-        <v>30</v>
-      </c>
-      <c r="G52" s="2" t="n">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>Ter -15</t>
-        </is>
-      </c>
-      <c r="B53" t="n">
-        <v>624</v>
-      </c>
-      <c r="C53" t="n">
-        <v>72</v>
-      </c>
-      <c r="D53" t="n">
-        <v>38</v>
-      </c>
-      <c r="E53" t="n">
-        <v>59</v>
-      </c>
-      <c r="F53" t="n">
-        <v>40</v>
-      </c>
-      <c r="G53" t="n">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>Ter +15</t>
-        </is>
-      </c>
-      <c r="B54" t="n">
-        <v>518</v>
-      </c>
-      <c r="C54" t="n">
-        <v>57</v>
-      </c>
-      <c r="D54" t="n">
-        <v>27</v>
-      </c>
-      <c r="E54" t="n">
-        <v>49</v>
-      </c>
-      <c r="F54" t="n">
-        <v>34</v>
-      </c>
-      <c r="G54" t="n">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="n">
-        <v>2022</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="1" t="inlineStr">
-        <is>
-          <t>habilidad</t>
-        </is>
-      </c>
-      <c r="B57" s="1" t="inlineStr">
-        <is>
-          <t>Central</t>
-        </is>
-      </c>
-      <c r="C57" s="1" t="inlineStr">
-        <is>
-          <t>Chorotega</t>
-        </is>
-      </c>
-      <c r="D57" s="1" t="inlineStr">
-        <is>
-          <t>Pacífico Central</t>
-        </is>
-      </c>
-      <c r="E57" s="1" t="inlineStr">
-        <is>
-          <t>Brunca</t>
-        </is>
-      </c>
-      <c r="F57" s="1" t="inlineStr">
-        <is>
-          <t>Huetar Caribe</t>
-        </is>
-      </c>
-      <c r="G57" s="1" t="inlineStr">
-        <is>
-          <t>Huetar Norte</t>
-        </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>P Inc</t>
+          <t>P Comp +15</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>25</v>
-      </c>
-      <c r="C58" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="D58" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="E58" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="F58" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="G58" s="2" t="n">
-        <v>6</v>
+        <v>353</v>
+      </c>
+      <c r="C58" t="n">
+        <v>53</v>
+      </c>
+      <c r="D58" t="n">
+        <v>42</v>
+      </c>
+      <c r="E58" t="n">
+        <v>69</v>
+      </c>
+      <c r="F58" t="n">
+        <v>80</v>
+      </c>
+      <c r="G58" t="n">
+        <v>61</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>P Comp</t>
+          <t>S Inc -15</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>167</v>
+        <v>252</v>
       </c>
       <c r="C59" t="n">
-        <v>25</v>
+        <v>48</v>
       </c>
       <c r="D59" t="n">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="E59" t="n">
-        <v>23</v>
+        <v>49</v>
       </c>
       <c r="F59" t="n">
-        <v>29</v>
+        <v>43</v>
       </c>
       <c r="G59" t="n">
-        <v>25</v>
+        <v>46</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>S Inc -15</t>
+          <t>S Inc+15</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>63</v>
-      </c>
-      <c r="C60" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="D60" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="E60" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="F60" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="G60" s="2" t="n">
-        <v>3</v>
+        <v>282</v>
+      </c>
+      <c r="C60" t="n">
+        <v>59</v>
+      </c>
+      <c r="D60" t="n">
+        <v>43</v>
+      </c>
+      <c r="E60" t="n">
+        <v>33</v>
+      </c>
+      <c r="F60" t="n">
+        <v>52</v>
+      </c>
+      <c r="G60" t="n">
+        <v>24</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>S Inc+15</t>
+          <t>S Comp -15</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>170</v>
+        <v>367</v>
       </c>
       <c r="C61" t="n">
-        <v>27</v>
-      </c>
-      <c r="D61" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="E61" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="F61" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="G61" s="2" t="n">
-        <v>16</v>
+        <v>66</v>
+      </c>
+      <c r="D61" t="n">
+        <v>30</v>
+      </c>
+      <c r="E61" t="n">
+        <v>43</v>
+      </c>
+      <c r="F61" t="n">
+        <v>46</v>
+      </c>
+      <c r="G61" t="n">
+        <v>29</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>S Comp -15</t>
+          <t>S Comp +15</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>277</v>
+        <v>269</v>
       </c>
       <c r="C62" t="n">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="D62" t="n">
         <v>24</v>
       </c>
       <c r="E62" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="F62" t="n">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="G62" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>S Comp +15</t>
+          <t>Ter -15</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>202</v>
+        <v>531</v>
       </c>
       <c r="C63" t="n">
-        <v>46</v>
+        <v>31</v>
       </c>
       <c r="D63" t="n">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="E63" t="n">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="F63" t="n">
-        <v>30</v>
-      </c>
-      <c r="G63" s="2" t="n">
-        <v>20</v>
+        <v>31</v>
+      </c>
+      <c r="G63" t="n">
+        <v>24</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Ter -15</t>
+          <t>Ter +15</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>557</v>
+        <v>454</v>
       </c>
       <c r="C64" t="n">
-        <v>55</v>
+        <v>43</v>
       </c>
       <c r="D64" t="n">
         <v>29</v>
       </c>
       <c r="E64" t="n">
-        <v>43</v>
-      </c>
-      <c r="F64" t="n">
-        <v>48</v>
+        <v>25</v>
+      </c>
+      <c r="F64" s="2" t="n">
+        <v>19</v>
       </c>
       <c r="G64" t="n">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>Ter +15</t>
-        </is>
-      </c>
-      <c r="B65" t="n">
-        <v>541</v>
-      </c>
-      <c r="C65" t="n">
-        <v>65</v>
-      </c>
-      <c r="D65" t="n">
-        <v>36</v>
-      </c>
-      <c r="E65" t="n">
-        <v>57</v>
-      </c>
-      <c r="F65" t="n">
-        <v>48</v>
-      </c>
-      <c r="G65" t="n">
-        <v>32</v>
+        <v>22</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>2022</v>
       </c>
     </row>
     <row r="67">
-      <c r="A67" t="n">
-        <v>2023</v>
+      <c r="A67" s="1" t="inlineStr">
+        <is>
+          <t>habilidad</t>
+        </is>
+      </c>
+      <c r="B67" s="1" t="inlineStr">
+        <is>
+          <t>Central</t>
+        </is>
+      </c>
+      <c r="C67" s="1" t="inlineStr">
+        <is>
+          <t>Chorotega</t>
+        </is>
+      </c>
+      <c r="D67" s="1" t="inlineStr">
+        <is>
+          <t>Pacífico Central</t>
+        </is>
+      </c>
+      <c r="E67" s="1" t="inlineStr">
+        <is>
+          <t>Brunca</t>
+        </is>
+      </c>
+      <c r="F67" s="1" t="inlineStr">
+        <is>
+          <t>Huetar Caribe</t>
+        </is>
+      </c>
+      <c r="G67" s="1" t="inlineStr">
+        <is>
+          <t>Huetar Norte</t>
+        </is>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="inlineStr">
-        <is>
-          <t>habilidad</t>
-        </is>
-      </c>
-      <c r="B68" s="1" t="inlineStr">
-        <is>
-          <t>Central</t>
-        </is>
-      </c>
-      <c r="C68" s="1" t="inlineStr">
-        <is>
-          <t>Chorotega</t>
-        </is>
-      </c>
-      <c r="D68" s="1" t="inlineStr">
-        <is>
-          <t>Pacífico Central</t>
-        </is>
-      </c>
-      <c r="E68" s="1" t="inlineStr">
-        <is>
-          <t>Brunca</t>
-        </is>
-      </c>
-      <c r="F68" s="1" t="inlineStr">
-        <is>
-          <t>Huetar Caribe</t>
-        </is>
-      </c>
-      <c r="G68" s="1" t="inlineStr">
-        <is>
-          <t>Huetar Norte</t>
-        </is>
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>P Inc -15</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C68" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D68" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="E68" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F68" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G68" s="2" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>P Inc</t>
+          <t>P Inc +15</t>
         </is>
       </c>
       <c r="B69" t="n">
+        <v>53</v>
+      </c>
+      <c r="C69" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="D69" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="E69" t="n">
         <v>30</v>
       </c>
-      <c r="C69" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="D69" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="E69" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="F69" s="2" t="n">
-        <v>9</v>
+      <c r="F69" t="n">
+        <v>31</v>
       </c>
       <c r="G69" s="2" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>P Comp</t>
+          <t>P Comp -15</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>197</v>
-      </c>
-      <c r="C70" t="n">
-        <v>24</v>
-      </c>
-      <c r="D70" t="n">
-        <v>28</v>
+        <v>72</v>
+      </c>
+      <c r="C70" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="D70" s="2" t="n">
+        <v>7</v>
       </c>
       <c r="E70" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="F70" t="n">
-        <v>27</v>
-      </c>
-      <c r="G70" t="n">
-        <v>25</v>
+        <v>10</v>
+      </c>
+      <c r="F70" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="G70" s="2" t="n">
+        <v>18</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>S Inc -15</t>
+          <t>P Comp +15</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>70</v>
-      </c>
-      <c r="C71" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="D71" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="E71" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="F71" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="G71" s="2" t="n">
-        <v>9</v>
+        <v>310</v>
+      </c>
+      <c r="C71" t="n">
+        <v>56</v>
+      </c>
+      <c r="D71" t="n">
+        <v>50</v>
+      </c>
+      <c r="E71" t="n">
+        <v>65</v>
+      </c>
+      <c r="F71" t="n">
+        <v>71</v>
+      </c>
+      <c r="G71" t="n">
+        <v>49</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>S Inc+15</t>
+          <t>S Inc -15</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>167</v>
+        <v>139</v>
       </c>
       <c r="C72" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="D72" t="n">
-        <v>22</v>
-      </c>
-      <c r="E72" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="F72" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="G72" s="2" t="n">
-        <v>16</v>
+        <v>26</v>
+      </c>
+      <c r="E72" t="n">
+        <v>25</v>
+      </c>
+      <c r="F72" t="n">
+        <v>47</v>
+      </c>
+      <c r="G72" t="n">
+        <v>27</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>S Comp -15</t>
+          <t>S Inc+15</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>311</v>
+        <v>237</v>
       </c>
       <c r="C73" t="n">
+        <v>43</v>
+      </c>
+      <c r="D73" t="n">
+        <v>28</v>
+      </c>
+      <c r="E73" t="n">
         <v>29</v>
       </c>
-      <c r="D73" t="n">
-        <v>26</v>
-      </c>
-      <c r="E73" t="n">
-        <v>31</v>
-      </c>
       <c r="F73" t="n">
-        <v>55</v>
+        <v>43</v>
       </c>
       <c r="G73" t="n">
         <v>24</v>
@@ -2071,76 +2104,393 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>S Comp +15</t>
+          <t>S Comp -15</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>223</v>
+        <v>377</v>
       </c>
       <c r="C74" t="n">
-        <v>39</v>
+        <v>57</v>
       </c>
       <c r="D74" t="n">
-        <v>27</v>
-      </c>
-      <c r="E74" s="2" t="n">
-        <v>18</v>
+        <v>35</v>
+      </c>
+      <c r="E74" t="n">
+        <v>41</v>
       </c>
       <c r="F74" t="n">
-        <v>25</v>
-      </c>
-      <c r="G74" s="2" t="n">
-        <v>14</v>
+        <v>49</v>
+      </c>
+      <c r="G74" t="n">
+        <v>41</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Ter -15</t>
+          <t>S Comp +15</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>515</v>
+        <v>288</v>
       </c>
       <c r="C75" t="n">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="D75" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E75" t="n">
-        <v>41</v>
+        <v>23</v>
       </c>
       <c r="F75" t="n">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="G75" t="n">
-        <v>36</v>
+        <v>23</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
+          <t>Ter -15</t>
+        </is>
+      </c>
+      <c r="B76" t="n">
+        <v>426</v>
+      </c>
+      <c r="C76" t="n">
+        <v>36</v>
+      </c>
+      <c r="D76" t="n">
+        <v>24</v>
+      </c>
+      <c r="E76" t="n">
+        <v>44</v>
+      </c>
+      <c r="F76" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="G76" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
           <t>Ter +15</t>
         </is>
       </c>
-      <c r="B76" t="n">
-        <v>561</v>
-      </c>
-      <c r="C76" t="n">
-        <v>61</v>
-      </c>
-      <c r="D76" t="n">
+      <c r="B77" t="n">
+        <v>430</v>
+      </c>
+      <c r="C77" t="n">
+        <v>50</v>
+      </c>
+      <c r="D77" t="n">
+        <v>26</v>
+      </c>
+      <c r="E77" t="n">
+        <v>28</v>
+      </c>
+      <c r="F77" t="n">
+        <v>26</v>
+      </c>
+      <c r="G77" s="2" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>2023</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="1" t="inlineStr">
+        <is>
+          <t>habilidad</t>
+        </is>
+      </c>
+      <c r="B80" s="1" t="inlineStr">
+        <is>
+          <t>Central</t>
+        </is>
+      </c>
+      <c r="C80" s="1" t="inlineStr">
+        <is>
+          <t>Chorotega</t>
+        </is>
+      </c>
+      <c r="D80" s="1" t="inlineStr">
+        <is>
+          <t>Pacífico Central</t>
+        </is>
+      </c>
+      <c r="E80" s="1" t="inlineStr">
+        <is>
+          <t>Brunca</t>
+        </is>
+      </c>
+      <c r="F80" s="1" t="inlineStr">
+        <is>
+          <t>Huetar Caribe</t>
+        </is>
+      </c>
+      <c r="G80" s="1" t="inlineStr">
+        <is>
+          <t>Huetar Norte</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>P Inc -15</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="C81" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D81" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E81" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="F81" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G81" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>P Inc +15</t>
+        </is>
+      </c>
+      <c r="B82" t="n">
+        <v>42</v>
+      </c>
+      <c r="C82" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="D82" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="E82" t="n">
+        <v>26</v>
+      </c>
+      <c r="F82" t="n">
+        <v>29</v>
+      </c>
+      <c r="G82" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>P Comp -15</t>
+        </is>
+      </c>
+      <c r="B83" t="n">
+        <v>54</v>
+      </c>
+      <c r="C83" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="D83" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="E83" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F83" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="G83" s="2" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>P Comp +15</t>
+        </is>
+      </c>
+      <c r="B84" t="n">
+        <v>292</v>
+      </c>
+      <c r="C84" t="n">
+        <v>50</v>
+      </c>
+      <c r="D84" t="n">
+        <v>47</v>
+      </c>
+      <c r="E84" t="n">
+        <v>50</v>
+      </c>
+      <c r="F84" t="n">
+        <v>68</v>
+      </c>
+      <c r="G84" t="n">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>S Inc -15</t>
+        </is>
+      </c>
+      <c r="B85" t="n">
+        <v>130</v>
+      </c>
+      <c r="C85" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="D85" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="E85" t="n">
+        <v>27</v>
+      </c>
+      <c r="F85" t="n">
+        <v>36</v>
+      </c>
+      <c r="G85" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>S Inc+15</t>
+        </is>
+      </c>
+      <c r="B86" t="n">
+        <v>255</v>
+      </c>
+      <c r="C86" t="n">
+        <v>29</v>
+      </c>
+      <c r="D86" t="n">
+        <v>28</v>
+      </c>
+      <c r="E86" t="n">
         <v>33</v>
       </c>
-      <c r="E76" t="n">
-        <v>52</v>
-      </c>
-      <c r="F76" t="n">
-        <v>49</v>
-      </c>
-      <c r="G76" t="n">
-        <v>35</v>
+      <c r="F86" t="n">
+        <v>36</v>
+      </c>
+      <c r="G86" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>S Comp -15</t>
+        </is>
+      </c>
+      <c r="B87" t="n">
+        <v>413</v>
+      </c>
+      <c r="C87" t="n">
+        <v>54</v>
+      </c>
+      <c r="D87" t="n">
+        <v>33</v>
+      </c>
+      <c r="E87" t="n">
+        <v>51</v>
+      </c>
+      <c r="F87" t="n">
+        <v>70</v>
+      </c>
+      <c r="G87" t="n">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>S Comp +15</t>
+        </is>
+      </c>
+      <c r="B88" t="n">
+        <v>317</v>
+      </c>
+      <c r="C88" t="n">
+        <v>41</v>
+      </c>
+      <c r="D88" t="n">
+        <v>32</v>
+      </c>
+      <c r="E88" t="n">
+        <v>26</v>
+      </c>
+      <c r="F88" t="n">
+        <v>54</v>
+      </c>
+      <c r="G88" s="2" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Ter -15</t>
+        </is>
+      </c>
+      <c r="B89" t="n">
+        <v>431</v>
+      </c>
+      <c r="C89" t="n">
+        <v>41</v>
+      </c>
+      <c r="D89" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="E89" t="n">
+        <v>37</v>
+      </c>
+      <c r="F89" t="n">
+        <v>26</v>
+      </c>
+      <c r="G89" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Ter +15</t>
+        </is>
+      </c>
+      <c r="B90" t="n">
+        <v>460</v>
+      </c>
+      <c r="C90" t="n">
+        <v>40</v>
+      </c>
+      <c r="D90" t="n">
+        <v>27</v>
+      </c>
+      <c r="E90" t="n">
+        <v>32</v>
+      </c>
+      <c r="F90" t="n">
+        <v>25</v>
+      </c>
+      <c r="G90" t="n">
+        <v>24</v>
       </c>
     </row>
   </sheetData>
@@ -2154,7 +2504,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2197,201 +2547,251 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>P Inc</t>
+          <t>P Inc -15</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>319</v>
-      </c>
-      <c r="C2" t="n">
-        <v>63</v>
-      </c>
-      <c r="D2" t="n">
-        <v>67</v>
+        <v>56</v>
+      </c>
+      <c r="C2" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="D2" s="2" t="n">
+        <v>18</v>
       </c>
       <c r="E2" t="n">
-        <v>86</v>
+        <v>21</v>
       </c>
       <c r="F2" t="n">
-        <v>110</v>
-      </c>
-      <c r="G2" t="n">
-        <v>70</v>
+        <v>33</v>
+      </c>
+      <c r="G2" s="2" t="n">
+        <v>19</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>P Comp</t>
+          <t>P Inc +15</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1810</v>
+        <v>546</v>
       </c>
       <c r="C3" t="n">
-        <v>248</v>
+        <v>126</v>
       </c>
       <c r="D3" t="n">
-        <v>217</v>
+        <v>149</v>
       </c>
       <c r="E3" t="n">
-        <v>249</v>
+        <v>225</v>
       </c>
       <c r="F3" t="n">
-        <v>331</v>
+        <v>276</v>
       </c>
       <c r="G3" t="n">
-        <v>219</v>
+        <v>174</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>S Inc -15</t>
+          <t>P Comp -15</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>796</v>
+        <v>763</v>
       </c>
       <c r="C4" t="n">
         <v>96</v>
       </c>
       <c r="D4" t="n">
-        <v>78</v>
+        <v>103</v>
       </c>
       <c r="E4" t="n">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="F4" t="n">
-        <v>109</v>
+        <v>158</v>
       </c>
       <c r="G4" t="n">
-        <v>91</v>
+        <v>158</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>S Inc+15</t>
+          <t>P Comp +15</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1390</v>
+        <v>2781</v>
       </c>
       <c r="C5" t="n">
-        <v>190</v>
+        <v>451</v>
       </c>
       <c r="D5" t="n">
-        <v>158</v>
+        <v>364</v>
       </c>
       <c r="E5" t="n">
-        <v>134</v>
+        <v>520</v>
       </c>
       <c r="F5" t="n">
-        <v>160</v>
+        <v>613</v>
       </c>
       <c r="G5" t="n">
-        <v>128</v>
+        <v>406</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>S Comp -15</t>
+          <t>S Inc -15</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2061</v>
+        <v>1697</v>
       </c>
       <c r="C6" t="n">
-        <v>215</v>
+        <v>286</v>
       </c>
       <c r="D6" t="n">
-        <v>151</v>
+        <v>236</v>
       </c>
       <c r="E6" t="n">
-        <v>218</v>
+        <v>301</v>
       </c>
       <c r="F6" t="n">
-        <v>259</v>
+        <v>358</v>
       </c>
       <c r="G6" t="n">
-        <v>167</v>
+        <v>308</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>S Comp +15</t>
+          <t>S Inc+15</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1387</v>
+        <v>1947</v>
       </c>
       <c r="C7" t="n">
-        <v>250</v>
+        <v>320</v>
       </c>
       <c r="D7" t="n">
-        <v>152</v>
+        <v>232</v>
       </c>
       <c r="E7" t="n">
-        <v>117</v>
+        <v>217</v>
       </c>
       <c r="F7" t="n">
-        <v>172</v>
+        <v>297</v>
       </c>
       <c r="G7" t="n">
-        <v>85</v>
+        <v>160</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Ter -15</t>
+          <t>S Comp -15</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4283</v>
+        <v>2575</v>
       </c>
       <c r="C8" t="n">
-        <v>424</v>
+        <v>383</v>
       </c>
       <c r="D8" t="n">
-        <v>241</v>
+        <v>223</v>
       </c>
       <c r="E8" t="n">
-        <v>377</v>
+        <v>303</v>
       </c>
       <c r="F8" t="n">
-        <v>339</v>
+        <v>353</v>
       </c>
       <c r="G8" t="n">
-        <v>237</v>
+        <v>278</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>S Comp +15</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>1914</v>
+      </c>
+      <c r="C9" t="n">
+        <v>288</v>
+      </c>
+      <c r="D9" t="n">
+        <v>192</v>
+      </c>
+      <c r="E9" t="n">
+        <v>191</v>
+      </c>
+      <c r="F9" t="n">
+        <v>272</v>
+      </c>
+      <c r="G9" t="n">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Ter -15</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>3593</v>
+      </c>
+      <c r="C10" t="n">
+        <v>276</v>
+      </c>
+      <c r="D10" t="n">
+        <v>175</v>
+      </c>
+      <c r="E10" t="n">
+        <v>300</v>
+      </c>
+      <c r="F10" t="n">
+        <v>226</v>
+      </c>
+      <c r="G10" t="n">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
           <t>Ter +15</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>3512</v>
-      </c>
-      <c r="C9" t="n">
-        <v>422</v>
-      </c>
-      <c r="D9" t="n">
-        <v>226</v>
-      </c>
-      <c r="E9" t="n">
-        <v>325</v>
-      </c>
-      <c r="F9" t="n">
-        <v>260</v>
-      </c>
-      <c r="G9" t="n">
-        <v>179</v>
+      <c r="B11" t="n">
+        <v>3060</v>
+      </c>
+      <c r="C11" t="n">
+        <v>328</v>
+      </c>
+      <c r="D11" t="n">
+        <v>170</v>
+      </c>
+      <c r="E11" t="n">
+        <v>201</v>
+      </c>
+      <c r="F11" t="n">
+        <v>153</v>
+      </c>
+      <c r="G11" t="n">
+        <v>142</v>
       </c>
     </row>
   </sheetData>
